--- a/backend/assets/vnutour-report-template.xlsx
+++ b/backend/assets/vnutour-report-template.xlsx
@@ -395,10 +395,17 @@
     <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="28" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="24" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="16" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="28" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="14" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="26" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="16" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="24" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="24" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="28" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="20" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
@@ -415,16 +422,37 @@
         <x:v>Đăng ký muộn</x:v>
       </x:c>
       <x:c r="E1" s="14" t="str">
+        <x:v>Đội trưởng</x:v>
+      </x:c>
+      <x:c r="F1" s="14" t="str">
         <x:v>MSSV</x:v>
       </x:c>
-      <x:c r="F1" s="14" t="str">
+      <x:c r="G1" s="14" t="str">
         <x:v>Họ tên</x:v>
       </x:c>
-      <x:c r="G1" s="14" t="str">
+      <x:c r="H1" s="14" t="str">
+        <x:v>Ngày sinh</x:v>
+      </x:c>
+      <x:c r="I1" s="14" t="str">
+        <x:v>Email</x:v>
+      </x:c>
+      <x:c r="J1" s="14" t="str">
+        <x:v>SĐT</x:v>
+      </x:c>
+      <x:c r="K1" s="14" t="str">
+        <x:v>CCCD</x:v>
+      </x:c>
+      <x:c r="L1" s="14" t="str">
         <x:v>Trường</x:v>
       </x:c>
-      <x:c r="H1" s="14" t="str">
-        <x:v>Đội trưởng</x:v>
+      <x:c r="M1" s="14" t="str">
+        <x:v>Khoa</x:v>
+      </x:c>
+      <x:c r="N1" s="14" t="str">
+        <x:v>Facebook</x:v>
+      </x:c>
+      <x:c r="O1" s="14" t="str">
+        <x:v>Discord</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="22" customHeight="1">
@@ -436,6 +464,13 @@
       <x:c r="F2" s="18" t="str"/>
       <x:c r="G2" s="18" t="str"/>
       <x:c r="H2" s="18" t="str"/>
+      <x:c r="I2" s="18" t="str"/>
+      <x:c r="J2" s="18" t="str"/>
+      <x:c r="K2" s="18" t="str"/>
+      <x:c r="L2" s="18" t="str"/>
+      <x:c r="M2" s="18" t="str"/>
+      <x:c r="N2" s="18" t="str"/>
+      <x:c r="O2" s="18" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
